--- a/2026_DSAIML_Club_Batch/01 Advanced Excel/2026_03_19.xlsx
+++ b/2026_DSAIML_Club_Batch/01 Advanced Excel/2026_03_19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\all_batches\2026_DSAIML_Club_Batch\01 Advanced Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A32E21-9599-4FA8-8EB7-EC50790A2674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE65F451-1A4B-415B-841F-9868E6A767D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,11 @@
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v2.0" hidden="1">Charts!$A$24:$A$30</definedName>
-    <definedName name="_xlchart.v2.1" hidden="1">Charts!$B$24:$B$30</definedName>
+    <definedName name="_xlchart.v2.1" hidden="1">Charts!$B$23</definedName>
+    <definedName name="_xlchart.v2.2" hidden="1">Charts!$B$24:$B$30</definedName>
+    <definedName name="_xlchart.v2.3" hidden="1">Charts!$A$24:$A$30</definedName>
+    <definedName name="_xlchart.v2.4" hidden="1">Charts!$B$23</definedName>
+    <definedName name="_xlchart.v2.5" hidden="1">Charts!$B$24:$B$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -352,7 +356,7 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
+  <c:roundedCorners val="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
       <c14:style val="102"/>
@@ -363,6 +367,47 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:ln w="9525" cmpd="dbl">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" baseline="0">
+                <a:ln w="9525" cmpd="dbl">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:ln>
+              </a:rPr>
+              <a:t>Sales in Lacs</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.39211111111111113"/>
+          <c:y val="7.407407407407407E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -377,11 +422,13 @@
         <a:p>
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:ln w="1270">
-                <a:noFill/>
+              <a:ln w="9525" cmpd="dbl">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
               </a:ln>
               <a:solidFill>
-                <a:srgbClr val="0070C0"/>
+                <a:srgbClr val="FF0000"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -432,7 +479,17 @@
       </c:spPr>
     </c:backWall>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="6.6580927384076991E-2"/>
+          <c:y val="0.1902314814814815"/>
+          <c:w val="0.77567519685039366"/>
+          <c:h val="0.70236913094196562"/>
+        </c:manualLayout>
+      </c:layout>
       <c:line3DChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -457,7 +514,13 @@
             <a:ln>
               <a:noFill/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                <a:prstClr val="black">
+                  <a:alpha val="40000"/>
+                </a:prstClr>
+              </a:outerShdw>
+            </a:effectLst>
             <a:sp3d/>
           </c:spPr>
           <c:cat>
@@ -541,7 +604,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E9DD-48DB-98EB-BD9E40A2003F}"/>
+              <c16:uniqueId val="{00000000-FFD2-4347-8CAA-3DE99F5BE3B1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -553,12 +616,12 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="471342880"/>
-        <c:axId val="471341440"/>
-        <c:axId val="465383168"/>
+        <c:axId val="1114394159"/>
+        <c:axId val="1114401839"/>
+        <c:axId val="1239650991"/>
       </c:line3DChart>
       <c:catAx>
-        <c:axId val="471342880"/>
+        <c:axId val="1114394159"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -587,11 +650,13 @@
           <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:ln w="1270">
-                  <a:noFill/>
+                <a:ln w="9525" cmpd="dbl">
+                  <a:solidFill>
+                    <a:srgbClr val="00B0F0"/>
+                  </a:solidFill>
                 </a:ln>
                 <a:solidFill>
-                  <a:srgbClr val="0070C0"/>
+                  <a:srgbClr val="FF0000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -601,7 +666,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="471341440"/>
+        <c:crossAx val="1114401839"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -609,7 +674,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="471341440"/>
+        <c:axId val="1114401839"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -646,11 +711,13 @@
           <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:ln w="1270">
-                  <a:noFill/>
+                <a:ln w="9525" cmpd="dbl">
+                  <a:solidFill>
+                    <a:srgbClr val="00B0F0"/>
+                  </a:solidFill>
                 </a:ln>
                 <a:solidFill>
-                  <a:srgbClr val="0070C0"/>
+                  <a:srgbClr val="FF0000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -660,12 +727,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="471342880"/>
+        <c:crossAx val="1114394159"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:serAx>
-        <c:axId val="465383168"/>
+        <c:axId val="1239650991"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -687,11 +754,13 @@
           <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:ln w="1270">
-                  <a:noFill/>
+                <a:ln w="9525" cmpd="dbl">
+                  <a:solidFill>
+                    <a:srgbClr val="00B0F0"/>
+                  </a:solidFill>
                 </a:ln>
                 <a:solidFill>
-                  <a:srgbClr val="0070C0"/>
+                  <a:srgbClr val="FF0000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -701,22 +770,56 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="471341440"/>
-        <c:crosses val="autoZero"/>
+        <c:crossAx val="1114401839"/>
       </c:serAx>
       <c:spPr>
-        <a:noFill/>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="5000"/>
+                <a:lumOff val="95000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="74000">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="45000"/>
+                <a:lumOff val="55000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="83000">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="45000"/>
+                <a:lumOff val="55000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="accent1">
+                <a:lumMod val="30000"/>
+                <a:lumOff val="70000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="1"/>
+        </a:gradFill>
         <a:ln>
-          <a:noFill/>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
         </a:ln>
-        <a:effectLst>
-          <a:softEdge rad="152400"/>
-        </a:effectLst>
+        <a:effectLst/>
       </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:gradFill>
@@ -748,32 +851,31 @@
       </a:gsLst>
       <a:lin ang="5400000" scaled="1"/>
     </a:gradFill>
-    <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
     <a:effectLst>
-      <a:glow rad="139700">
+      <a:glow rad="177800">
         <a:schemeClr val="accent2">
           <a:satMod val="175000"/>
           <a:alpha val="40000"/>
         </a:schemeClr>
       </a:glow>
-      <a:outerShdw blurRad="228600" dist="266700" dir="2700000" algn="l" rotWithShape="0">
+      <a:outerShdw blurRad="254000" dist="254000" dir="2700000" algn="tl" rotWithShape="0">
         <a:prstClr val="black">
           <a:alpha val="40000"/>
         </a:prstClr>
       </a:outerShdw>
-      <a:softEdge rad="203200"/>
     </a:effectLst>
     <a:scene3d>
       <a:camera prst="orthographicFront"/>
       <a:lightRig rig="threePt" dir="t"/>
     </a:scene3d>
     <a:sp3d>
-      <a:bevelT w="165100" prst="coolSlant"/>
+      <a:bevelT prst="relaxedInset"/>
     </a:sp3d>
   </c:spPr>
   <c:txPr>
@@ -782,11 +884,13 @@
     <a:p>
       <a:pPr>
         <a:defRPr>
-          <a:ln w="1270">
-            <a:noFill/>
+          <a:ln w="9525" cmpd="dbl">
+            <a:solidFill>
+              <a:srgbClr val="00B0F0"/>
+            </a:solidFill>
           </a:ln>
           <a:solidFill>
-            <a:srgbClr val="0070C0"/>
+            <a:srgbClr val="FF0000"/>
           </a:solidFill>
         </a:defRPr>
       </a:pPr>
@@ -836,6 +940,13 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="10800000" algn="r" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
@@ -848,7 +959,7 @@
     <c:autoTitleDeleted val="0"/>
     <c:view3D>
       <c:rotX val="30"/>
-      <c:rotY val="20"/>
+      <c:rotY val="10"/>
       <c:depthPercent val="100"/>
       <c:rAngAx val="0"/>
     </c:view3D>
@@ -890,20 +1001,32 @@
       <c:pie3DChart>
         <c:varyColors val="1"/>
         <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
+          <c:idx val="0"/>
+          <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Charts!$B$1</c:f>
+              <c:f>Charts!$A$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Sales in Lacs</c:v>
+                  <c:v>Year</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:explosion val="10"/>
+          <c:spPr>
+            <a:scene3d>
+              <a:camera prst="orthographicFront"/>
+              <a:lightRig rig="threePt" dir="t"/>
+            </a:scene3d>
+            <a:sp3d>
+              <a:bevelT prst="relaxedInset"/>
+              <a:contourClr>
+                <a:srgbClr val="000000"/>
+              </a:contourClr>
+            </a:sp3d>
+          </c:spPr>
+          <c:explosion val="15"/>
           <c:dPt>
             <c:idx val="0"/>
             <c:bubble3D val="0"/>
@@ -917,7 +1040,12 @@
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
               <a:sp3d contourW="25400">
+                <a:bevelT prst="relaxedInset"/>
                 <a:contourClr>
                   <a:schemeClr val="lt1"/>
                 </a:contourClr>
@@ -925,7 +1053,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-B38A-432E-91F6-4A28FA22D0A5}"/>
+                <c16:uniqueId val="{00000003-48DD-4233-B93C-525AC5AD49C9}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -942,17 +1070,17 @@
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
               <a:sp3d contourW="25400">
+                <a:bevelT prst="relaxedInset"/>
                 <a:contourClr>
                   <a:schemeClr val="lt1"/>
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-B38A-432E-91F6-4A28FA22D0A5}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -967,17 +1095,17 @@
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
               <a:sp3d contourW="25400">
+                <a:bevelT prst="relaxedInset"/>
                 <a:contourClr>
                   <a:schemeClr val="lt1"/>
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-B38A-432E-91F6-4A28FA22D0A5}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -992,17 +1120,17 @@
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
               <a:sp3d contourW="25400">
+                <a:bevelT prst="relaxedInset"/>
                 <a:contourClr>
                   <a:schemeClr val="lt1"/>
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-B38A-432E-91F6-4A28FA22D0A5}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -1017,17 +1145,17 @@
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
               <a:sp3d contourW="25400">
+                <a:bevelT prst="relaxedInset"/>
                 <a:contourClr>
                   <a:schemeClr val="lt1"/>
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-B38A-432E-91F6-4A28FA22D0A5}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -1042,17 +1170,17 @@
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
               <a:sp3d contourW="25400">
+                <a:bevelT prst="relaxedInset"/>
                 <a:contourClr>
                   <a:schemeClr val="lt1"/>
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-B38A-432E-91F6-4A28FA22D0A5}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -1069,17 +1197,17 @@
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
               <a:sp3d contourW="25400">
+                <a:bevelT prst="relaxedInset"/>
                 <a:contourClr>
                   <a:schemeClr val="lt1"/>
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-B38A-432E-91F6-4A28FA22D0A5}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -1096,17 +1224,17 @@
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
               <a:sp3d contourW="25400">
+                <a:bevelT prst="relaxedInset"/>
                 <a:contourClr>
                   <a:schemeClr val="lt1"/>
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-B38A-432E-91F6-4A28FA22D0A5}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
@@ -1123,17 +1251,17 @@
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
               <a:sp3d contourW="25400">
+                <a:bevelT prst="relaxedInset"/>
                 <a:contourClr>
                   <a:schemeClr val="lt1"/>
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-B38A-432E-91F6-4A28FA22D0A5}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
@@ -1150,19 +1278,89 @@
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
               <a:sp3d contourW="25400">
+                <a:bevelT prst="relaxedInset"/>
                 <a:contourClr>
                   <a:schemeClr val="lt1"/>
                 </a:contourClr>
               </a:sp3d>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-B38A-432E-91F6-4A28FA22D0A5}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:numFmt formatCode="&quot;₹&quot;#,##0.00_);[Red]\(&quot;₹&quot;#,##0.00\)" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:sysClr val="window" lastClr="FFFFFF"/>
+                </a:solidFill>
+                <a:ln>
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="25000"/>
+                      <a:lumOff val="75000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:effectLst>
+                        <a:outerShdw blurRad="50800" dist="38100" dir="10800000" algn="r" rotWithShape="0">
+                          <a:prstClr val="black">
+                            <a:alpha val="40000"/>
+                          </a:prstClr>
+                        </a:outerShdw>
+                      </a:effectLst>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <a:prstGeom prst="wedgeRectCallout">
+                      <a:avLst/>
+                    </a:prstGeom>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                  </c15:spPr>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-48DD-4233-B93C-525AC5AD49C9}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
             <c:spPr>
               <a:solidFill>
                 <a:sysClr val="window" lastClr="FFFFFF"/>
@@ -1178,7 +1376,7 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
@@ -1191,6 +1389,13 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
+                    <a:effectLst>
+                      <a:outerShdw blurRad="50800" dist="38100" dir="10800000" algn="r" rotWithShape="0">
+                        <a:prstClr val="black">
+                          <a:alpha val="40000"/>
+                        </a:prstClr>
+                      </a:outerShdw>
+                    </a:effectLst>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
                     <a:cs typeface="+mn-cs"/>
@@ -1204,7 +1409,7 @@
             <c:showVal val="0"/>
             <c:showCatName val="1"/>
             <c:showSerName val="0"/>
-            <c:showPercent val="1"/>
+            <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="0"/>
             <c:extLst>
@@ -1262,46 +1467,46 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Charts!$B$2:$B$11</c:f>
+              <c:f>Charts!$A$2:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>15</c:v>
+                  <c:v>2001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>20</c:v>
+                  <c:v>2002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>28</c:v>
+                  <c:v>2003</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>27</c:v>
+                  <c:v>2004</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>22</c:v>
+                  <c:v>2005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>26</c:v>
+                  <c:v>2006</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>30</c:v>
+                  <c:v>2007</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>38</c:v>
+                  <c:v>2008</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>55</c:v>
+                  <c:v>2009</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>46</c:v>
+                  <c:v>2010</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3454-4A96-BF6A-6FFAC98DA461}"/>
+              <c16:uniqueId val="{00000000-48DD-4233-B93C-525AC5AD49C9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1318,37 +1523,25 @@
           <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
             <c15:filteredPieSeries>
               <c15:ser>
-                <c:idx val="0"/>
-                <c:order val="0"/>
+                <c:idx val="1"/>
+                <c:order val="1"/>
                 <c:tx>
                   <c:strRef>
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Charts!$A$1</c15:sqref>
+                          <c15:sqref>Charts!$B$1</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>Year</c:v>
+                        <c:v>Sales in Lacs</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
                 </c:tx>
-                <c:spPr>
-                  <a:scene3d>
-                    <a:camera prst="orthographicFront"/>
-                    <a:lightRig rig="threePt" dir="t"/>
-                  </a:scene3d>
-                  <a:sp3d>
-                    <a:bevelT prst="relaxedInset"/>
-                    <a:contourClr>
-                      <a:srgbClr val="000000"/>
-                    </a:contourClr>
-                  </a:sp3d>
-                </c:spPr>
                 <c:dPt>
                   <c:idx val="0"/>
                   <c:bubble3D val="0"/>
@@ -1362,22 +1555,12 @@
                       </a:solidFill>
                     </a:ln>
                     <a:effectLst/>
-                    <a:scene3d>
-                      <a:camera prst="orthographicFront"/>
-                      <a:lightRig rig="threePt" dir="t"/>
-                    </a:scene3d>
                     <a:sp3d contourW="25400">
-                      <a:bevelT prst="relaxedInset"/>
                       <a:contourClr>
                         <a:schemeClr val="lt1"/>
                       </a:contourClr>
                     </a:sp3d>
                   </c:spPr>
-                  <c:extLst>
-                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                      <c16:uniqueId val="{00000015-B38A-432E-91F6-4A28FA22D0A5}"/>
-                    </c:ext>
-                  </c:extLst>
                 </c:dPt>
                 <c:dPt>
                   <c:idx val="1"/>
@@ -1392,22 +1575,12 @@
                       </a:solidFill>
                     </a:ln>
                     <a:effectLst/>
-                    <a:scene3d>
-                      <a:camera prst="orthographicFront"/>
-                      <a:lightRig rig="threePt" dir="t"/>
-                    </a:scene3d>
                     <a:sp3d contourW="25400">
-                      <a:bevelT prst="relaxedInset"/>
                       <a:contourClr>
                         <a:schemeClr val="lt1"/>
                       </a:contourClr>
                     </a:sp3d>
                   </c:spPr>
-                  <c:extLst>
-                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                      <c16:uniqueId val="{00000017-B38A-432E-91F6-4A28FA22D0A5}"/>
-                    </c:ext>
-                  </c:extLst>
                 </c:dPt>
                 <c:dPt>
                   <c:idx val="2"/>
@@ -1422,22 +1595,12 @@
                       </a:solidFill>
                     </a:ln>
                     <a:effectLst/>
-                    <a:scene3d>
-                      <a:camera prst="orthographicFront"/>
-                      <a:lightRig rig="threePt" dir="t"/>
-                    </a:scene3d>
                     <a:sp3d contourW="25400">
-                      <a:bevelT prst="relaxedInset"/>
                       <a:contourClr>
                         <a:schemeClr val="lt1"/>
                       </a:contourClr>
                     </a:sp3d>
                   </c:spPr>
-                  <c:extLst>
-                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                      <c16:uniqueId val="{00000019-B38A-432E-91F6-4A28FA22D0A5}"/>
-                    </c:ext>
-                  </c:extLst>
                 </c:dPt>
                 <c:dPt>
                   <c:idx val="3"/>
@@ -1452,22 +1615,12 @@
                       </a:solidFill>
                     </a:ln>
                     <a:effectLst/>
-                    <a:scene3d>
-                      <a:camera prst="orthographicFront"/>
-                      <a:lightRig rig="threePt" dir="t"/>
-                    </a:scene3d>
                     <a:sp3d contourW="25400">
-                      <a:bevelT prst="relaxedInset"/>
                       <a:contourClr>
                         <a:schemeClr val="lt1"/>
                       </a:contourClr>
                     </a:sp3d>
                   </c:spPr>
-                  <c:extLst>
-                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                      <c16:uniqueId val="{0000001B-B38A-432E-91F6-4A28FA22D0A5}"/>
-                    </c:ext>
-                  </c:extLst>
                 </c:dPt>
                 <c:dPt>
                   <c:idx val="4"/>
@@ -1482,22 +1635,12 @@
                       </a:solidFill>
                     </a:ln>
                     <a:effectLst/>
-                    <a:scene3d>
-                      <a:camera prst="orthographicFront"/>
-                      <a:lightRig rig="threePt" dir="t"/>
-                    </a:scene3d>
                     <a:sp3d contourW="25400">
-                      <a:bevelT prst="relaxedInset"/>
                       <a:contourClr>
                         <a:schemeClr val="lt1"/>
                       </a:contourClr>
                     </a:sp3d>
                   </c:spPr>
-                  <c:extLst>
-                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                      <c16:uniqueId val="{0000001D-B38A-432E-91F6-4A28FA22D0A5}"/>
-                    </c:ext>
-                  </c:extLst>
                 </c:dPt>
                 <c:dPt>
                   <c:idx val="5"/>
@@ -1512,22 +1655,12 @@
                       </a:solidFill>
                     </a:ln>
                     <a:effectLst/>
-                    <a:scene3d>
-                      <a:camera prst="orthographicFront"/>
-                      <a:lightRig rig="threePt" dir="t"/>
-                    </a:scene3d>
                     <a:sp3d contourW="25400">
-                      <a:bevelT prst="relaxedInset"/>
                       <a:contourClr>
                         <a:schemeClr val="lt1"/>
                       </a:contourClr>
                     </a:sp3d>
                   </c:spPr>
-                  <c:extLst>
-                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                      <c16:uniqueId val="{0000001F-B38A-432E-91F6-4A28FA22D0A5}"/>
-                    </c:ext>
-                  </c:extLst>
                 </c:dPt>
                 <c:dPt>
                   <c:idx val="6"/>
@@ -1544,22 +1677,12 @@
                       </a:solidFill>
                     </a:ln>
                     <a:effectLst/>
-                    <a:scene3d>
-                      <a:camera prst="orthographicFront"/>
-                      <a:lightRig rig="threePt" dir="t"/>
-                    </a:scene3d>
                     <a:sp3d contourW="25400">
-                      <a:bevelT prst="relaxedInset"/>
                       <a:contourClr>
                         <a:schemeClr val="lt1"/>
                       </a:contourClr>
                     </a:sp3d>
                   </c:spPr>
-                  <c:extLst>
-                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                      <c16:uniqueId val="{00000021-B38A-432E-91F6-4A28FA22D0A5}"/>
-                    </c:ext>
-                  </c:extLst>
                 </c:dPt>
                 <c:dPt>
                   <c:idx val="7"/>
@@ -1576,22 +1699,12 @@
                       </a:solidFill>
                     </a:ln>
                     <a:effectLst/>
-                    <a:scene3d>
-                      <a:camera prst="orthographicFront"/>
-                      <a:lightRig rig="threePt" dir="t"/>
-                    </a:scene3d>
                     <a:sp3d contourW="25400">
-                      <a:bevelT prst="relaxedInset"/>
                       <a:contourClr>
                         <a:schemeClr val="lt1"/>
                       </a:contourClr>
                     </a:sp3d>
                   </c:spPr>
-                  <c:extLst>
-                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                      <c16:uniqueId val="{00000023-B38A-432E-91F6-4A28FA22D0A5}"/>
-                    </c:ext>
-                  </c:extLst>
                 </c:dPt>
                 <c:dPt>
                   <c:idx val="8"/>
@@ -1608,22 +1721,12 @@
                       </a:solidFill>
                     </a:ln>
                     <a:effectLst/>
-                    <a:scene3d>
-                      <a:camera prst="orthographicFront"/>
-                      <a:lightRig rig="threePt" dir="t"/>
-                    </a:scene3d>
                     <a:sp3d contourW="25400">
-                      <a:bevelT prst="relaxedInset"/>
                       <a:contourClr>
                         <a:schemeClr val="lt1"/>
                       </a:contourClr>
                     </a:sp3d>
                   </c:spPr>
-                  <c:extLst>
-                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                      <c16:uniqueId val="{00000025-B38A-432E-91F6-4A28FA22D0A5}"/>
-                    </c:ext>
-                  </c:extLst>
                 </c:dPt>
                 <c:dPt>
                   <c:idx val="9"/>
@@ -1640,82 +1743,13 @@
                       </a:solidFill>
                     </a:ln>
                     <a:effectLst/>
-                    <a:scene3d>
-                      <a:camera prst="orthographicFront"/>
-                      <a:lightRig rig="threePt" dir="t"/>
-                    </a:scene3d>
                     <a:sp3d contourW="25400">
-                      <a:bevelT prst="relaxedInset"/>
                       <a:contourClr>
                         <a:schemeClr val="lt1"/>
                       </a:contourClr>
                     </a:sp3d>
                   </c:spPr>
-                  <c:extLst>
-                    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                      <c16:uniqueId val="{00000027-B38A-432E-91F6-4A28FA22D0A5}"/>
-                    </c:ext>
-                  </c:extLst>
                 </c:dPt>
-                <c:dLbls>
-                  <c:spPr>
-                    <a:solidFill>
-                      <a:sysClr val="window" lastClr="FFFFFF"/>
-                    </a:solidFill>
-                    <a:ln>
-                      <a:solidFill>
-                        <a:sysClr val="windowText" lastClr="000000">
-                          <a:lumMod val="25000"/>
-                          <a:lumOff val="75000"/>
-                        </a:sysClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                  <c:txPr>
-                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                      <a:spAutoFit/>
-                    </a:bodyPr>
-                    <a:lstStyle/>
-                    <a:p>
-                      <a:pPr>
-                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                          <a:solidFill>
-                            <a:schemeClr val="dk1">
-                              <a:lumMod val="65000"/>
-                              <a:lumOff val="35000"/>
-                            </a:schemeClr>
-                          </a:solidFill>
-                          <a:latin typeface="+mn-lt"/>
-                          <a:ea typeface="+mn-ea"/>
-                          <a:cs typeface="+mn-cs"/>
-                        </a:defRPr>
-                      </a:pPr>
-                      <a:endParaRPr lang="en-US"/>
-                    </a:p>
-                  </c:txPr>
-                  <c:dLblPos val="outEnd"/>
-                  <c:showLegendKey val="0"/>
-                  <c:showVal val="0"/>
-                  <c:showCatName val="1"/>
-                  <c:showSerName val="0"/>
-                  <c:showPercent val="1"/>
-                  <c:showBubbleSize val="0"/>
-                  <c:showLeaderLines val="0"/>
-                  <c:extLst>
-                    <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                      <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                        <a:prstGeom prst="wedgeRectCallout">
-                          <a:avLst/>
-                        </a:prstGeom>
-                        <a:noFill/>
-                        <a:ln>
-                          <a:noFill/>
-                        </a:ln>
-                      </c15:spPr>
-                    </c:ext>
-                  </c:extLst>
-                </c:dLbls>
                 <c:cat>
                   <c:numRef>
                     <c:extLst>
@@ -1766,7 +1800,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Charts!$A$2:$A$11</c15:sqref>
+                          <c15:sqref>Charts!$B$2:$B$11</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -1774,41 +1808,41 @@
                       <c:formatCode>General</c:formatCode>
                       <c:ptCount val="10"/>
                       <c:pt idx="0">
-                        <c:v>2001</c:v>
+                        <c:v>15</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>2002</c:v>
+                        <c:v>20</c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v>2003</c:v>
+                        <c:v>28</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>2004</c:v>
+                        <c:v>27</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>2005</c:v>
+                        <c:v>22</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>2006</c:v>
+                        <c:v>26</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>2007</c:v>
+                        <c:v>30</c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v>2008</c:v>
+                        <c:v>38</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>2009</c:v>
+                        <c:v>55</c:v>
                       </c:pt>
                       <c:pt idx="9">
-                        <c:v>2010</c:v>
+                        <c:v>46</c:v>
                       </c:pt>
                     </c:numCache>
                   </c:numRef>
                 </c:val>
                 <c:extLst>
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000000-3454-4A96-BF6A-6FFAC98DA461}"/>
+                    <c16:uniqueId val="{00000001-48DD-4233-B93C-525AC5AD49C9}"/>
                   </c:ext>
                 </c:extLst>
               </c15:ser>
@@ -1824,37 +1858,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr rtl="0">
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -1867,9 +1870,21 @@
     </c:extLst>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="100000">
+          <a:srgbClr val="7030A0"/>
+        </a:gs>
+        <a:gs pos="0">
+          <a:schemeClr val="accent1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:lin ang="13500000" scaled="1"/>
+      <a:tileRect/>
+    </a:gradFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
@@ -1880,20 +1895,21 @@
       <a:round/>
     </a:ln>
     <a:effectLst/>
-    <a:scene3d>
-      <a:camera prst="orthographicFront"/>
-      <a:lightRig rig="threePt" dir="t"/>
-    </a:scene3d>
-    <a:sp3d>
-      <a:bevelT prst="relaxedInset"/>
-    </a:sp3d>
   </c:spPr>
   <c:txPr>
     <a:bodyPr/>
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:effectLst>
+            <a:outerShdw blurRad="50800" dist="38100" dir="10800000" algn="r" rotWithShape="0">
+              <a:prstClr val="black">
+                <a:alpha val="40000"/>
+              </a:prstClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -1914,7 +1930,7 @@
         <cx:f>_xlchart.v2.0</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v2.1</cx:f>
+        <cx:f>_xlchart.v2.2</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -1922,12 +1938,21 @@
     <cx:title pos="t" align="ctr" overlay="0"/>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="funnel" uniqueId="{C31D0D35-EAAB-4267-A430-F26013A80026}">
+        <cx:series layoutId="funnel" uniqueId="{8795CD40-0A6E-45FB-A1E9-66E1E7767ED2}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v2.1</cx:f>
+              <cx:v>Numbers</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataLabels>
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
           <cx:dataId val="0"/>
         </cx:series>
       </cx:plotAreaRegion>
-      <cx:axis id="0">
-        <cx:catScaling gapWidth="0"/>
+      <cx:axis id="1">
+        <cx:catScaling gapWidth="0.0599999987"/>
         <cx:tickLabels/>
       </cx:axis>
     </cx:plotArea>
@@ -2056,7 +2081,7 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -2164,11 +2189,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -2179,11 +2199,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -2215,9 +2230,6 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3091,7 +3103,7 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="366">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -3603,22 +3615,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
+      <xdr:colOff>457200</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>140970</xdr:rowOff>
+      <xdr:rowOff>148590</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
+      <xdr:colOff>152400</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>140970</xdr:rowOff>
+      <xdr:rowOff>148590</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4">
+        <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDA214E5-6692-4C88-4CE7-EB316251E882}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85C33445-A943-BA59-1A42-71C766DBD4FF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3639,22 +3651,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>556260</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>26670</xdr:rowOff>
+      <xdr:colOff>350520</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>251460</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>26670</xdr:rowOff>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart 5">
+        <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45B46E29-01A7-F988-2E7B-95B55AB8419F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0847E3E1-D67E-47DF-CEF6-C04BAF204716}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3674,25 +3686,25 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>163830</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>480060</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>125730</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>167640</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>30480</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>125730</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx2="http://schemas.microsoft.com/office/drawing/2015/10/21/chartex" Requires="cx2">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="7" name="Chart 6">
+            <xdr:cNvPr id="4" name="Chart 3">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEC1EF68-D70E-381D-581E-C0A2426C6071}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C67C9BA-C8D8-6666-6039-A1AD9BD8EE10}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3719,8 +3731,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2727960" y="3638550"/>
-              <a:ext cx="5013960" cy="3158490"/>
+              <a:off x="2567940" y="3234690"/>
+              <a:ext cx="4572000" cy="2743200"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
